--- a/trajectory.xlsx
+++ b/trajectory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mk.rio.guniawan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B432D0F3-2A12-442C-93AA-5491A02A1480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C0C9D9-1EB2-485B-91B8-40E3D9C6892F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29205" yWindow="2355" windowWidth="19875" windowHeight="13575" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31260" yWindow="1320" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -502,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F48806B-EBAC-4EEB-9504-69ABA76D2D25}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
@@ -533,7 +533,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -544,585 +544,2389 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>214.86</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1">
-        <v>300.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>394.03</v>
+        <v>90</v>
       </c>
       <c r="B5" s="1">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="C5" s="1">
-        <v>294.95999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>576.16999999999905</v>
+        <v>120</v>
       </c>
       <c r="B6" s="1">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1">
-        <v>295.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>708.30999999999904</v>
+        <v>150</v>
       </c>
       <c r="B7" s="1">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1">
-        <v>296.45999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>893.729999999999</v>
+        <v>180</v>
       </c>
       <c r="B8" s="1">
-        <v>0.41</v>
+        <v>0.9</v>
       </c>
       <c r="C8" s="1">
-        <v>294.45</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>1077.94</v>
+        <v>210</v>
       </c>
       <c r="B9" s="1">
-        <v>0.48</v>
+        <v>1.8</v>
       </c>
       <c r="C9" s="1">
-        <v>308.97000000000003</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>1266.79</v>
+        <v>240</v>
       </c>
       <c r="B10" s="1">
-        <v>0.56999999999999995</v>
+        <v>2.7</v>
       </c>
       <c r="C10" s="1">
-        <v>309.85000000000002</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>1390.32</v>
+        <v>270</v>
       </c>
       <c r="B11" s="1">
-        <v>0.26</v>
+        <v>3.6</v>
       </c>
       <c r="C11" s="1">
-        <v>96.33</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>1511.36</v>
+        <v>300</v>
       </c>
       <c r="B12" s="1">
-        <v>0.51</v>
+        <v>4.5</v>
       </c>
       <c r="C12" s="1">
-        <v>105.78</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>1633.89</v>
+        <v>330</v>
       </c>
       <c r="B13" s="1">
-        <v>0.61</v>
+        <v>5.4</v>
       </c>
       <c r="C13" s="1">
-        <v>117.72</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>1693.29</v>
+        <v>360</v>
       </c>
       <c r="B14" s="1">
-        <v>1.06</v>
+        <v>6.3</v>
       </c>
       <c r="C14" s="1">
-        <v>96.08</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>1753.05</v>
+        <v>390</v>
       </c>
       <c r="B15" s="1">
-        <v>3.34</v>
+        <v>7.2</v>
       </c>
       <c r="C15" s="1">
-        <v>89.02</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>1812.62</v>
+        <v>420</v>
       </c>
       <c r="B16" s="1">
-        <v>5.19</v>
+        <v>8.1</v>
       </c>
       <c r="C16" s="1">
-        <v>84.82</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>1871.78</v>
+        <v>450</v>
       </c>
       <c r="B17" s="1">
-        <v>6.15</v>
+        <v>9</v>
       </c>
       <c r="C17" s="1">
-        <v>82.89</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>1931.94</v>
+        <v>480</v>
       </c>
       <c r="B18" s="1">
-        <v>7.49</v>
+        <v>9.9</v>
       </c>
       <c r="C18" s="1">
-        <v>82.57</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>1992.27</v>
+        <v>510</v>
       </c>
       <c r="B19" s="1">
-        <v>8.56</v>
+        <v>10.8</v>
       </c>
       <c r="C19" s="1">
-        <v>80.34</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>2056.0500000000002</v>
+        <v>540</v>
       </c>
       <c r="B20" s="1">
-        <v>10.27</v>
+        <v>11.7</v>
       </c>
       <c r="C20" s="1">
-        <v>74.53</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>2118.92</v>
+        <v>570</v>
       </c>
       <c r="B21" s="1">
-        <v>12.28</v>
+        <v>12.6</v>
       </c>
       <c r="C21" s="1">
-        <v>74.150000000000006</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>2181.35</v>
+        <v>600</v>
       </c>
       <c r="B22" s="1">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="C22" s="1">
-        <v>75.03</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>2240.9699999999998</v>
+        <v>630</v>
       </c>
       <c r="B23" s="1">
-        <v>14.57</v>
+        <v>14.4</v>
       </c>
       <c r="C23" s="1">
-        <v>76.319999999999993</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>2299.85</v>
+        <v>660</v>
       </c>
       <c r="B24" s="1">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="C24" s="1">
-        <v>76.59</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>2363.19</v>
+        <v>666.64</v>
       </c>
       <c r="B25" s="1">
-        <v>16.52</v>
+        <v>15.5</v>
       </c>
       <c r="C25" s="1">
-        <v>76.010000000000005</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>2425.8200000000002</v>
+        <v>690</v>
       </c>
       <c r="B26" s="1">
-        <v>18.43</v>
+        <v>15.5</v>
       </c>
       <c r="C26" s="1">
-        <v>71.89</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>2487.87</v>
+        <v>720</v>
       </c>
       <c r="B27" s="1">
-        <v>20.260000000000002</v>
+        <v>15.5</v>
       </c>
       <c r="C27" s="1">
-        <v>69.3</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>2549.33</v>
+        <v>750</v>
       </c>
       <c r="B28" s="1">
-        <v>21.12</v>
+        <v>15.5</v>
       </c>
       <c r="C28" s="1">
-        <v>68.75</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>2611.85</v>
+        <v>780</v>
       </c>
       <c r="B29" s="1">
-        <v>23.23</v>
+        <v>15.5</v>
       </c>
       <c r="C29" s="1">
-        <v>64.81</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>2671.99</v>
+        <v>810</v>
       </c>
       <c r="B30" s="1">
-        <v>26.06</v>
+        <v>15.5</v>
       </c>
       <c r="C30" s="1">
-        <v>60.34</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>2732.05</v>
+        <v>840</v>
       </c>
       <c r="B31" s="1">
-        <v>28.88</v>
+        <v>15.5</v>
       </c>
       <c r="C31" s="1">
-        <v>56.49</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>2792.79</v>
+        <v>870</v>
       </c>
       <c r="B32" s="1">
-        <v>30.8</v>
+        <v>15.5</v>
       </c>
       <c r="C32" s="1">
-        <v>52.09</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>2852.22</v>
+        <v>900</v>
       </c>
       <c r="B33" s="1">
-        <v>31.92</v>
+        <v>15.5</v>
       </c>
       <c r="C33" s="1">
-        <v>47.18</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>2912.03</v>
+        <v>930</v>
       </c>
       <c r="B34" s="1">
-        <v>32.61</v>
+        <v>15.5</v>
       </c>
       <c r="C34" s="1">
-        <v>41.02</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>2973.22</v>
+        <v>960</v>
       </c>
       <c r="B35" s="1">
-        <v>31.86</v>
+        <v>15.5</v>
       </c>
       <c r="C35" s="1">
-        <v>34.39</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>3033.53</v>
+        <v>990</v>
       </c>
       <c r="B36" s="1">
-        <v>31.35</v>
+        <v>15.5</v>
       </c>
       <c r="C36" s="1">
-        <v>28.68</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>3096.87</v>
+        <v>1020</v>
       </c>
       <c r="B37" s="1">
-        <v>31.22</v>
+        <v>15.5</v>
       </c>
       <c r="C37" s="1">
-        <v>24.54</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>3159.36</v>
+        <v>1050</v>
       </c>
       <c r="B38" s="1">
-        <v>32.25</v>
+        <v>15.5</v>
       </c>
       <c r="C38" s="1">
-        <v>19.97</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>3218.41</v>
+        <v>1080</v>
       </c>
       <c r="B39" s="1">
-        <v>31.47</v>
+        <v>15.5</v>
       </c>
       <c r="C39" s="1">
-        <v>13.62</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>3283.37</v>
+        <v>1110</v>
       </c>
       <c r="B40" s="1">
-        <v>32.29</v>
+        <v>15.5</v>
       </c>
       <c r="C40" s="1">
-        <v>7.34</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>3346.75</v>
+        <v>1140</v>
       </c>
       <c r="B41" s="1">
-        <v>32.97</v>
+        <v>15.5</v>
       </c>
       <c r="C41" s="1">
-        <v>2.2000000000000002</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>3409.15</v>
+        <v>1170</v>
       </c>
       <c r="B42" s="1">
-        <v>31.16</v>
+        <v>15.5</v>
       </c>
       <c r="C42" s="1">
-        <v>356.54</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>3471.81</v>
+        <v>1200</v>
       </c>
       <c r="B43" s="1">
-        <v>31.39</v>
+        <v>15.5</v>
       </c>
       <c r="C43" s="1">
-        <v>349.99</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>3534.1</v>
+        <v>1230</v>
       </c>
       <c r="B44" s="1">
-        <v>32.15</v>
+        <v>15.5</v>
       </c>
       <c r="C44" s="1">
-        <v>343.29</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>3598.86</v>
+        <v>1260</v>
       </c>
       <c r="B45" s="1">
-        <v>32.630000000000003</v>
+        <v>15.5</v>
       </c>
       <c r="C45" s="1">
-        <v>336.24</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>3660.4</v>
+        <v>1290</v>
       </c>
       <c r="B46" s="1">
-        <v>35.39</v>
+        <v>15.5</v>
       </c>
       <c r="C46" s="1">
-        <v>334.79</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>3733.47</v>
+        <v>1320</v>
       </c>
       <c r="B47" s="1">
-        <v>37.729999999999997</v>
+        <v>15.5</v>
       </c>
       <c r="C47" s="1">
-        <v>334.31</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>3783.56</v>
+        <v>1350</v>
       </c>
       <c r="B48" s="1">
-        <v>39.42</v>
+        <v>15.5</v>
       </c>
       <c r="C48" s="1">
-        <v>334.12</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>3846.38</v>
+        <v>1380</v>
       </c>
       <c r="B49" s="1">
-        <v>41.63</v>
+        <v>15.5</v>
       </c>
       <c r="C49" s="1">
-        <v>333.93</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>3908.86</v>
+        <v>1410</v>
       </c>
       <c r="B50" s="1">
-        <v>45.25</v>
+        <v>15.5</v>
       </c>
       <c r="C50" s="1">
-        <v>333.33</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>3975.81</v>
+        <v>1440</v>
       </c>
       <c r="B51" s="1">
-        <v>48.27</v>
+        <v>15.5</v>
       </c>
       <c r="C51" s="1">
-        <v>332.9</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>4035.65</v>
+        <v>1470</v>
       </c>
       <c r="B52" s="1">
-        <v>51.83</v>
+        <v>15.5</v>
       </c>
       <c r="C52" s="1">
-        <v>332.73</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>4097.08</v>
+        <v>1500</v>
       </c>
       <c r="B53" s="1">
-        <v>55.19</v>
+        <v>15.5</v>
       </c>
       <c r="C53" s="1">
-        <v>334.19</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>4159.21</v>
+        <v>1530</v>
       </c>
       <c r="B54" s="1">
-        <v>56.63</v>
+        <v>15.5</v>
       </c>
       <c r="C54" s="1">
-        <v>334.1</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>4222.76</v>
+        <v>1560</v>
       </c>
       <c r="B55" s="1">
-        <v>59.44</v>
+        <v>15.5</v>
       </c>
       <c r="C55" s="1">
-        <v>334.47</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>4283.0600000000004</v>
+        <v>1590</v>
       </c>
       <c r="B56" s="1">
-        <v>61.1</v>
+        <v>15.5</v>
       </c>
       <c r="C56" s="1">
-        <v>334.38</v>
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1620</v>
+      </c>
+      <c r="B57">
+        <v>15.5</v>
+      </c>
+      <c r="C57">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1650</v>
+      </c>
+      <c r="B58">
+        <v>15.5</v>
+      </c>
+      <c r="C58">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1680</v>
+      </c>
+      <c r="B59">
+        <v>15.5</v>
+      </c>
+      <c r="C59">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1710</v>
+      </c>
+      <c r="B60">
+        <v>15.5</v>
+      </c>
+      <c r="C60">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1740</v>
+      </c>
+      <c r="B61">
+        <v>15.5</v>
+      </c>
+      <c r="C61">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1770</v>
+      </c>
+      <c r="B62">
+        <v>15.5</v>
+      </c>
+      <c r="C62">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1800</v>
+      </c>
+      <c r="B63">
+        <v>15.5</v>
+      </c>
+      <c r="C63">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1830</v>
+      </c>
+      <c r="B64">
+        <v>15.5</v>
+      </c>
+      <c r="C64">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1860</v>
+      </c>
+      <c r="B65">
+        <v>15.5</v>
+      </c>
+      <c r="C65">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1890</v>
+      </c>
+      <c r="B66">
+        <v>15.5</v>
+      </c>
+      <c r="C66">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1920</v>
+      </c>
+      <c r="B67">
+        <v>15.5</v>
+      </c>
+      <c r="C67">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1950</v>
+      </c>
+      <c r="B68">
+        <v>15.5</v>
+      </c>
+      <c r="C68">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1959.7</v>
+      </c>
+      <c r="B69">
+        <v>15.5</v>
+      </c>
+      <c r="C69">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1980</v>
+      </c>
+      <c r="B70">
+        <v>15.5</v>
+      </c>
+      <c r="C70">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2010</v>
+      </c>
+      <c r="B71">
+        <v>15.5</v>
+      </c>
+      <c r="C71">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2040</v>
+      </c>
+      <c r="B72">
+        <v>15.5</v>
+      </c>
+      <c r="C72">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2070</v>
+      </c>
+      <c r="B73">
+        <v>15.5</v>
+      </c>
+      <c r="C73">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2100</v>
+      </c>
+      <c r="B74">
+        <v>15.5</v>
+      </c>
+      <c r="C74">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2130</v>
+      </c>
+      <c r="B75">
+        <v>15.5</v>
+      </c>
+      <c r="C75">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2160</v>
+      </c>
+      <c r="B76">
+        <v>15.5</v>
+      </c>
+      <c r="C76">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2190</v>
+      </c>
+      <c r="B77">
+        <v>15.5</v>
+      </c>
+      <c r="C77">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2220</v>
+      </c>
+      <c r="B78">
+        <v>15.5</v>
+      </c>
+      <c r="C78">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2250</v>
+      </c>
+      <c r="B79">
+        <v>15.5</v>
+      </c>
+      <c r="C79">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2280</v>
+      </c>
+      <c r="B80">
+        <v>15.5</v>
+      </c>
+      <c r="C80">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2310</v>
+      </c>
+      <c r="B81">
+        <v>15.5</v>
+      </c>
+      <c r="C81">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2340</v>
+      </c>
+      <c r="B82">
+        <v>15.5</v>
+      </c>
+      <c r="C82">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2370</v>
+      </c>
+      <c r="B83">
+        <v>15.5</v>
+      </c>
+      <c r="C83">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2400</v>
+      </c>
+      <c r="B84">
+        <v>15.5</v>
+      </c>
+      <c r="C84">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2430</v>
+      </c>
+      <c r="B85">
+        <v>15.5</v>
+      </c>
+      <c r="C85">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2460</v>
+      </c>
+      <c r="B86">
+        <v>15.5</v>
+      </c>
+      <c r="C86">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2490</v>
+      </c>
+      <c r="B87">
+        <v>15.5</v>
+      </c>
+      <c r="C87">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2520</v>
+      </c>
+      <c r="B88">
+        <v>15.5</v>
+      </c>
+      <c r="C88">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2550</v>
+      </c>
+      <c r="B89">
+        <v>15.5</v>
+      </c>
+      <c r="C89">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>2580</v>
+      </c>
+      <c r="B90">
+        <v>15.5</v>
+      </c>
+      <c r="C90">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2610</v>
+      </c>
+      <c r="B91">
+        <v>15.5</v>
+      </c>
+      <c r="C91">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>2640</v>
+      </c>
+      <c r="B92">
+        <v>15.5</v>
+      </c>
+      <c r="C92">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>2670</v>
+      </c>
+      <c r="B93">
+        <v>15.5</v>
+      </c>
+      <c r="C93">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>2700</v>
+      </c>
+      <c r="B94">
+        <v>15.5</v>
+      </c>
+      <c r="C94">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>2730</v>
+      </c>
+      <c r="B95">
+        <v>15.5</v>
+      </c>
+      <c r="C95">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>2760</v>
+      </c>
+      <c r="B96">
+        <v>15.5</v>
+      </c>
+      <c r="C96">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>2790</v>
+      </c>
+      <c r="B97">
+        <v>15.5</v>
+      </c>
+      <c r="C97">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>2820</v>
+      </c>
+      <c r="B98">
+        <v>15.5</v>
+      </c>
+      <c r="C98">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>2850</v>
+      </c>
+      <c r="B99">
+        <v>15.5</v>
+      </c>
+      <c r="C99">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>2880</v>
+      </c>
+      <c r="B100">
+        <v>15.5</v>
+      </c>
+      <c r="C100">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>2910</v>
+      </c>
+      <c r="B101">
+        <v>15.5</v>
+      </c>
+      <c r="C101">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2940</v>
+      </c>
+      <c r="B102">
+        <v>15.5</v>
+      </c>
+      <c r="C102">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2970</v>
+      </c>
+      <c r="B103">
+        <v>15.5</v>
+      </c>
+      <c r="C103">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>3000</v>
+      </c>
+      <c r="B104">
+        <v>15.5</v>
+      </c>
+      <c r="C104">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>3030</v>
+      </c>
+      <c r="B105">
+        <v>15.5</v>
+      </c>
+      <c r="C105">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>3060</v>
+      </c>
+      <c r="B106">
+        <v>15.5</v>
+      </c>
+      <c r="C106">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>3090</v>
+      </c>
+      <c r="B107">
+        <v>15.5</v>
+      </c>
+      <c r="C107">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>3120</v>
+      </c>
+      <c r="B108">
+        <v>15.5</v>
+      </c>
+      <c r="C108">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>3150</v>
+      </c>
+      <c r="B109">
+        <v>15.5</v>
+      </c>
+      <c r="C109">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>3180</v>
+      </c>
+      <c r="B110">
+        <v>15.5</v>
+      </c>
+      <c r="C110">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>3210</v>
+      </c>
+      <c r="B111">
+        <v>15.5</v>
+      </c>
+      <c r="C111">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>3240</v>
+      </c>
+      <c r="B112">
+        <v>15.5</v>
+      </c>
+      <c r="C112">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>3270</v>
+      </c>
+      <c r="B113">
+        <v>15.5</v>
+      </c>
+      <c r="C113">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>3300</v>
+      </c>
+      <c r="B114">
+        <v>15.5</v>
+      </c>
+      <c r="C114">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>3330</v>
+      </c>
+      <c r="B115">
+        <v>15.5</v>
+      </c>
+      <c r="C115">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>3360</v>
+      </c>
+      <c r="B116">
+        <v>15.5</v>
+      </c>
+      <c r="C116">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>3390</v>
+      </c>
+      <c r="B117">
+        <v>15.5</v>
+      </c>
+      <c r="C117">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>3420</v>
+      </c>
+      <c r="B118">
+        <v>15.5</v>
+      </c>
+      <c r="C118">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>3450</v>
+      </c>
+      <c r="B119">
+        <v>15.5</v>
+      </c>
+      <c r="C119">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>3480</v>
+      </c>
+      <c r="B120">
+        <v>15.5</v>
+      </c>
+      <c r="C120">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>3500.15</v>
+      </c>
+      <c r="B121">
+        <v>15.5</v>
+      </c>
+      <c r="C121">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>3510</v>
+      </c>
+      <c r="B122">
+        <v>15.5</v>
+      </c>
+      <c r="C122">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>3540</v>
+      </c>
+      <c r="B123">
+        <v>15.5</v>
+      </c>
+      <c r="C123">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>3570</v>
+      </c>
+      <c r="B124">
+        <v>15.5</v>
+      </c>
+      <c r="C124">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>3600</v>
+      </c>
+      <c r="B125">
+        <v>15.5</v>
+      </c>
+      <c r="C125">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>3630</v>
+      </c>
+      <c r="B126">
+        <v>15.5</v>
+      </c>
+      <c r="C126">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>3660</v>
+      </c>
+      <c r="B127">
+        <v>15.5</v>
+      </c>
+      <c r="C127">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>3690</v>
+      </c>
+      <c r="B128">
+        <v>15.5</v>
+      </c>
+      <c r="C128">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>3720</v>
+      </c>
+      <c r="B129">
+        <v>15.5</v>
+      </c>
+      <c r="C129">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>3750</v>
+      </c>
+      <c r="B130">
+        <v>15.5</v>
+      </c>
+      <c r="C130">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>3780</v>
+      </c>
+      <c r="B131">
+        <v>15.5</v>
+      </c>
+      <c r="C131">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>3810</v>
+      </c>
+      <c r="B132">
+        <v>15.5</v>
+      </c>
+      <c r="C132">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>3840</v>
+      </c>
+      <c r="B133">
+        <v>15.5</v>
+      </c>
+      <c r="C133">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>3870</v>
+      </c>
+      <c r="B134">
+        <v>15.5</v>
+      </c>
+      <c r="C134">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>3900</v>
+      </c>
+      <c r="B135">
+        <v>15.5</v>
+      </c>
+      <c r="C135">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>3930</v>
+      </c>
+      <c r="B136">
+        <v>15.5</v>
+      </c>
+      <c r="C136">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>3960</v>
+      </c>
+      <c r="B137">
+        <v>15.5</v>
+      </c>
+      <c r="C137">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>3990</v>
+      </c>
+      <c r="B138">
+        <v>15.5</v>
+      </c>
+      <c r="C138">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>4020</v>
+      </c>
+      <c r="B139">
+        <v>15.5</v>
+      </c>
+      <c r="C139">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>4050</v>
+      </c>
+      <c r="B140">
+        <v>15.5</v>
+      </c>
+      <c r="C140">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>4080</v>
+      </c>
+      <c r="B141">
+        <v>15.5</v>
+      </c>
+      <c r="C141">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>4110</v>
+      </c>
+      <c r="B142">
+        <v>15.5</v>
+      </c>
+      <c r="C142">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>4140</v>
+      </c>
+      <c r="B143">
+        <v>15.5</v>
+      </c>
+      <c r="C143">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>4170</v>
+      </c>
+      <c r="B144">
+        <v>15.5</v>
+      </c>
+      <c r="C144">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>4200</v>
+      </c>
+      <c r="B145">
+        <v>15.5</v>
+      </c>
+      <c r="C145">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>4230</v>
+      </c>
+      <c r="B146">
+        <v>15.5</v>
+      </c>
+      <c r="C146">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>4260</v>
+      </c>
+      <c r="B147">
+        <v>15.5</v>
+      </c>
+      <c r="C147">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>4290</v>
+      </c>
+      <c r="B148">
+        <v>15.5</v>
+      </c>
+      <c r="C148">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>4320</v>
+      </c>
+      <c r="B149">
+        <v>15.5</v>
+      </c>
+      <c r="C149">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>4350</v>
+      </c>
+      <c r="B150">
+        <v>15.5</v>
+      </c>
+      <c r="C150">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>4380</v>
+      </c>
+      <c r="B151">
+        <v>15.5</v>
+      </c>
+      <c r="C151">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>4410</v>
+      </c>
+      <c r="B152">
+        <v>15.5</v>
+      </c>
+      <c r="C152">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>4440</v>
+      </c>
+      <c r="B153">
+        <v>15.5</v>
+      </c>
+      <c r="C153">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>4470</v>
+      </c>
+      <c r="B154">
+        <v>15.5</v>
+      </c>
+      <c r="C154">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>4500</v>
+      </c>
+      <c r="B155">
+        <v>15.5</v>
+      </c>
+      <c r="C155">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>4530</v>
+      </c>
+      <c r="B156">
+        <v>15.5</v>
+      </c>
+      <c r="C156">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>4560</v>
+      </c>
+      <c r="B157">
+        <v>15.5</v>
+      </c>
+      <c r="C157">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>4590</v>
+      </c>
+      <c r="B158">
+        <v>15.5</v>
+      </c>
+      <c r="C158">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>4620</v>
+      </c>
+      <c r="B159">
+        <v>15.5</v>
+      </c>
+      <c r="C159">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>4650</v>
+      </c>
+      <c r="B160">
+        <v>15.5</v>
+      </c>
+      <c r="C160">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>4680</v>
+      </c>
+      <c r="B161">
+        <v>15.5</v>
+      </c>
+      <c r="C161">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>4710</v>
+      </c>
+      <c r="B162">
+        <v>15.5</v>
+      </c>
+      <c r="C162">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>4740</v>
+      </c>
+      <c r="B163">
+        <v>15.5</v>
+      </c>
+      <c r="C163">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>4770</v>
+      </c>
+      <c r="B164">
+        <v>15.5</v>
+      </c>
+      <c r="C164">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>4800</v>
+      </c>
+      <c r="B165">
+        <v>15.5</v>
+      </c>
+      <c r="C165">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>4830</v>
+      </c>
+      <c r="B166">
+        <v>15.5</v>
+      </c>
+      <c r="C166">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>4860</v>
+      </c>
+      <c r="B167">
+        <v>15.5</v>
+      </c>
+      <c r="C167">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>4884.12</v>
+      </c>
+      <c r="B168">
+        <v>15.5</v>
+      </c>
+      <c r="C168">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>4890</v>
+      </c>
+      <c r="B169">
+        <v>15.5</v>
+      </c>
+      <c r="C169">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>4920</v>
+      </c>
+      <c r="B170">
+        <v>15.5</v>
+      </c>
+      <c r="C170">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>4950</v>
+      </c>
+      <c r="B171">
+        <v>15.5</v>
+      </c>
+      <c r="C171">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>4980</v>
+      </c>
+      <c r="B172">
+        <v>15.5</v>
+      </c>
+      <c r="C172">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>5010</v>
+      </c>
+      <c r="B173">
+        <v>15.5</v>
+      </c>
+      <c r="C173">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>5040</v>
+      </c>
+      <c r="B174">
+        <v>15.5</v>
+      </c>
+      <c r="C174">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>5070</v>
+      </c>
+      <c r="B175">
+        <v>15.5</v>
+      </c>
+      <c r="C175">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>5100</v>
+      </c>
+      <c r="B176">
+        <v>15.5</v>
+      </c>
+      <c r="C176">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>5130</v>
+      </c>
+      <c r="B177">
+        <v>15.5</v>
+      </c>
+      <c r="C177">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>5160</v>
+      </c>
+      <c r="B178">
+        <v>15.5</v>
+      </c>
+      <c r="C178">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>5190</v>
+      </c>
+      <c r="B179">
+        <v>15.5</v>
+      </c>
+      <c r="C179">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>5220</v>
+      </c>
+      <c r="B180">
+        <v>15.5</v>
+      </c>
+      <c r="C180">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>5250</v>
+      </c>
+      <c r="B181">
+        <v>15.5</v>
+      </c>
+      <c r="C181">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>5280</v>
+      </c>
+      <c r="B182">
+        <v>15.5</v>
+      </c>
+      <c r="C182">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>5310</v>
+      </c>
+      <c r="B183">
+        <v>15.5</v>
+      </c>
+      <c r="C183">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>5340</v>
+      </c>
+      <c r="B184">
+        <v>15.5</v>
+      </c>
+      <c r="C184">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>5370</v>
+      </c>
+      <c r="B185">
+        <v>15.5</v>
+      </c>
+      <c r="C185">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>5400</v>
+      </c>
+      <c r="B186">
+        <v>15.5</v>
+      </c>
+      <c r="C186">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>5430</v>
+      </c>
+      <c r="B187">
+        <v>15.5</v>
+      </c>
+      <c r="C187">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>5460</v>
+      </c>
+      <c r="B188">
+        <v>15.5</v>
+      </c>
+      <c r="C188">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>5461.08</v>
+      </c>
+      <c r="B189">
+        <v>15.5</v>
+      </c>
+      <c r="C189">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>5490</v>
+      </c>
+      <c r="B190">
+        <v>15.5</v>
+      </c>
+      <c r="C190">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>5520</v>
+      </c>
+      <c r="B191">
+        <v>15.5</v>
+      </c>
+      <c r="C191">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>5545.94</v>
+      </c>
+      <c r="B192">
+        <v>15.5</v>
+      </c>
+      <c r="C192">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>5550</v>
+      </c>
+      <c r="B193">
+        <v>15.5</v>
+      </c>
+      <c r="C193">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>5580</v>
+      </c>
+      <c r="B194">
+        <v>15.5</v>
+      </c>
+      <c r="C194">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>5610</v>
+      </c>
+      <c r="B195">
+        <v>15.5</v>
+      </c>
+      <c r="C195">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>5640</v>
+      </c>
+      <c r="B196">
+        <v>15.5</v>
+      </c>
+      <c r="C196">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>5670</v>
+      </c>
+      <c r="B197">
+        <v>15.5</v>
+      </c>
+      <c r="C197">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>5700</v>
+      </c>
+      <c r="B198">
+        <v>15.5</v>
+      </c>
+      <c r="C198">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>5700.46</v>
+      </c>
+      <c r="B199">
+        <v>15.5</v>
+      </c>
+      <c r="C199">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>5730</v>
+      </c>
+      <c r="B200">
+        <v>15.5</v>
+      </c>
+      <c r="C200">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>5760</v>
+      </c>
+      <c r="B201">
+        <v>15.5</v>
+      </c>
+      <c r="C201">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>5790</v>
+      </c>
+      <c r="B202">
+        <v>15.5</v>
+      </c>
+      <c r="C202">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>5812.67</v>
+      </c>
+      <c r="B203">
+        <v>15.5</v>
+      </c>
+      <c r="C203">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>5820</v>
+      </c>
+      <c r="B204">
+        <v>15.5</v>
+      </c>
+      <c r="C204">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>5850</v>
+      </c>
+      <c r="B205">
+        <v>15.5</v>
+      </c>
+      <c r="C205">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>5880</v>
+      </c>
+      <c r="B206">
+        <v>15.5</v>
+      </c>
+      <c r="C206">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>5896.34</v>
+      </c>
+      <c r="B207">
+        <v>15.5</v>
+      </c>
+      <c r="C207">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>5910</v>
+      </c>
+      <c r="B208">
+        <v>15.5</v>
+      </c>
+      <c r="C208">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>5940</v>
+      </c>
+      <c r="B209">
+        <v>15.5</v>
+      </c>
+      <c r="C209">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>5941.52</v>
+      </c>
+      <c r="B210">
+        <v>15.5</v>
+      </c>
+      <c r="C210">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>5970</v>
+      </c>
+      <c r="B211">
+        <v>15.5</v>
+      </c>
+      <c r="C211">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>5992.74</v>
+      </c>
+      <c r="B212">
+        <v>15.5</v>
+      </c>
+      <c r="C212">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>5995.44</v>
+      </c>
+      <c r="B213">
+        <v>15.5</v>
+      </c>
+      <c r="C213">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>6000</v>
+      </c>
+      <c r="B214">
+        <v>15.5</v>
+      </c>
+      <c r="C214">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>6030</v>
+      </c>
+      <c r="B215">
+        <v>15.5</v>
+      </c>
+      <c r="C215">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>6060</v>
+      </c>
+      <c r="B216">
+        <v>15.5</v>
+      </c>
+      <c r="C216">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>6090</v>
+      </c>
+      <c r="B217">
+        <v>15.5</v>
+      </c>
+      <c r="C217">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>6120</v>
+      </c>
+      <c r="B218">
+        <v>15.5</v>
+      </c>
+      <c r="C218">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>6150</v>
+      </c>
+      <c r="B219">
+        <v>15.5</v>
+      </c>
+      <c r="C219">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>6151.1</v>
+      </c>
+      <c r="B220">
+        <v>15.5</v>
+      </c>
+      <c r="C220">
+        <v>15.49</v>
       </c>
     </row>
   </sheetData>
